--- a/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_9_6.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_9_6.xlsx
@@ -517,52 +517,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9748379928550344</v>
+        <v>0.9999970347421123</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6906922097153667</v>
+        <v>0.6616188094088302</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9776582740398512</v>
+        <v>0.9999998540361883</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9437523186175245</v>
+        <v>0.9999925115415463</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9576554077488417</v>
+        <v>0.9999975434463748</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1682584576387747</v>
+        <v>1.7603051745786e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>2.068342617864758</v>
+        <v>0.2008776920412408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1336698632018558</v>
+        <v>5.922703460030875e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6136616034620707</v>
+        <v>1.856869269182998e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3736657826118604</v>
+        <v>9.580481518916534e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5835835814266209</v>
+        <v>0.0004551402773565474</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4101931955052091</v>
+        <v>0.001326764928153665</v>
       </c>
       <c r="N2" t="n">
-        <v>1.006862365584991</v>
+        <v>1.000001581470873</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4276559690548389</v>
+        <v>0.001383248057927192</v>
       </c>
       <c r="P2" t="n">
-        <v>227.5645080868735</v>
+        <v>164.5000467385968</v>
       </c>
       <c r="Q2" t="n">
-        <v>364.078600472112</v>
+        <v>248.6024786545026</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +572,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9754803491214091</v>
+        <v>0.9999975854802722</v>
       </c>
       <c r="C3" t="n">
-        <v>0.689881072809835</v>
+        <v>0.6615237926002615</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9779722587552093</v>
+        <v>0.9999995379007756</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9406625689604721</v>
+        <v>0.9999943048349101</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9558518571203913</v>
+        <v>0.9999979490852062</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1639630183277482</v>
+        <v>1.433363212273532e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>2.073766694086991</v>
+        <v>0.2009340981233196</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1317913022516291</v>
+        <v>1.875037822389691e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6473707392387136</v>
+        <v>1.412196796405519e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3895810417094755</v>
+        <v>7.998502893222442e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>0.533464749886315</v>
+        <v>0.0004313784758995392</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4049234721867184</v>
+        <v>0.001197231478150125</v>
       </c>
       <c r="N3" t="n">
-        <v>1.006687177512343</v>
+        <v>1.000001287743855</v>
       </c>
       <c r="O3" t="n">
-        <v>0.422161902704849</v>
+        <v>0.001248200100785794</v>
       </c>
       <c r="P3" t="n">
-        <v>227.6162287491759</v>
+        <v>164.9109739567558</v>
       </c>
       <c r="Q3" t="n">
-        <v>364.1303211344144</v>
+        <v>249.0134058726617</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +627,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9752963073675062</v>
+        <v>0.9999979989458007</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6884480652216121</v>
+        <v>0.6614379696158399</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9752886136501567</v>
+        <v>0.9999990952364693</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9370911956049901</v>
+        <v>0.9999955763257784</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9527343782268008</v>
+        <v>0.9999981230178837</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1651937063835318</v>
+        <v>1.187912213777347e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>2.083349222427831</v>
+        <v>0.2009850463542323</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1478474688483626</v>
+        <v>3.671215510817157e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6863343844240876</v>
+        <v>1.096912638256701e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4170909344400536</v>
+        <v>7.320170946692087e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4882089176634231</v>
+        <v>0.0004111735884083415</v>
       </c>
       <c r="M4" t="n">
-        <v>0.406440286368775</v>
+        <v>0.001089913856126871</v>
       </c>
       <c r="N4" t="n">
-        <v>1.006737370717953</v>
+        <v>1.000001067228906</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4237432908068739</v>
+        <v>0.001136313745414907</v>
       </c>
       <c r="P4" t="n">
-        <v>227.6012730311459</v>
+        <v>165.2866264677619</v>
       </c>
       <c r="Q4" t="n">
-        <v>364.1153654163844</v>
+        <v>249.3890583836677</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9746096212067543</v>
+        <v>0.9999983053104504</v>
       </c>
       <c r="C5" t="n">
-        <v>0.686652663621114</v>
+        <v>0.6613604575020769</v>
       </c>
       <c r="D5" t="n">
-        <v>0.970878554526431</v>
+        <v>0.9999985696206511</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9333807287981262</v>
+        <v>0.9999964504993371</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9489456595872613</v>
+        <v>0.9999981274885635</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1697855799023779</v>
+        <v>1.006040923382105e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.095355081197426</v>
+        <v>0.2010310608933109</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1742327177244792</v>
+        <v>5.803981564334399e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7268155376792754</v>
+        <v>8.801489308776066e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4505241177646843</v>
+        <v>7.302735436555232e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4473899144386499</v>
+        <v>0.0003985767631041862</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4120504579567627</v>
+        <v>0.001003015913822959</v>
       </c>
       <c r="N5" t="n">
-        <v>1.006924648761794</v>
+        <v>1.000000903834426</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4295922990140185</v>
+        <v>0.001045716377803578</v>
       </c>
       <c r="P5" t="n">
-        <v>227.5464378654508</v>
+        <v>165.6189756156157</v>
       </c>
       <c r="Q5" t="n">
-        <v>364.0605302506893</v>
+        <v>249.7214075315215</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +737,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9736241604854957</v>
+        <v>0.9999985273038922</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6846598874850681</v>
+        <v>0.6612905126262505</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9655354950290039</v>
+        <v>0.9999979929943462</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9297139571385092</v>
+        <v>0.9999970124562274</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9448676583602755</v>
+        <v>0.9999980061674265</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1763753602830638</v>
+        <v>8.74256026786897e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.108680784395055</v>
+        <v>0.2010725831930628</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2062000793049761</v>
+        <v>8.143730419050571e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7668199773444251</v>
+        <v>7.40803765682814e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4865100474658276</v>
+        <v>7.775884037939356e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4113190127697853</v>
+        <v>0.000387195046877251</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4199706659792607</v>
+        <v>0.0009350165917174395</v>
       </c>
       <c r="N6" t="n">
-        <v>1.007193410776683</v>
+        <v>1.000000785437924</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4378496866891251</v>
+        <v>0.000974822183778025</v>
       </c>
       <c r="P6" t="n">
-        <v>227.4702816522015</v>
+        <v>165.8997851347227</v>
       </c>
       <c r="Q6" t="n">
-        <v>363.98437403744</v>
+        <v>250.0022170506286</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +792,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9724699162479655</v>
+        <v>0.9999986836567488</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6825779395504747</v>
+        <v>0.6612274951166779</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9597561737955943</v>
+        <v>0.999997391637693</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9261849868854256</v>
+        <v>0.9999973388810905</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9407269568553038</v>
+        <v>0.9999977971042777</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1840937968142342</v>
+        <v>7.81438216953765e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.122602779820169</v>
+        <v>0.2011099931089597</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2407775815108213</v>
+        <v>1.0583826419722e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8053210051352689</v>
+        <v>6.598621004836274e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5230492697410176</v>
+        <v>8.591223712279138e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>0.390182365219829</v>
+        <v>0.0003768968809856536</v>
       </c>
       <c r="M7" t="n">
-        <v>0.429061530335958</v>
+        <v>0.0008839899416587075</v>
       </c>
       <c r="N7" t="n">
-        <v>1.007508204659646</v>
+        <v>1.000000702049734</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4473275679621704</v>
+        <v>0.0009216232235865654</v>
       </c>
       <c r="P7" t="n">
-        <v>227.3846197719292</v>
+        <v>166.124259494422</v>
       </c>
       <c r="Q7" t="n">
-        <v>363.8987121571677</v>
+        <v>250.2266914103278</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +847,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9712318671924783</v>
+        <v>0.9999987890158003</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6804789175175048</v>
+        <v>0.6611706058340938</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9538522708948313</v>
+        <v>0.9999967827914558</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9228426808198671</v>
+        <v>0.9999974875816573</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9366594054443369</v>
+        <v>0.999997527645425</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1923726365489691</v>
+        <v>7.188925327195555e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.136638949819747</v>
+        <v>0.2011437650445907</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2761004520226919</v>
+        <v>1.305431254586434e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.841785528632777</v>
+        <v>6.229896901699325e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5589429860455211</v>
+        <v>9.642104723781832e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3708261178833845</v>
+        <v>0.0003677149860472127</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4386030512308015</v>
+        <v>0.0008478753049355521</v>
       </c>
       <c r="N8" t="n">
-        <v>1.007845854402051</v>
+        <v>1.00000064585824</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4572752911551786</v>
+        <v>0.0008839711120105012</v>
       </c>
       <c r="P8" t="n">
-        <v>227.2966419450879</v>
+        <v>166.2911079162051</v>
       </c>
       <c r="Q8" t="n">
-        <v>363.8107343303264</v>
+        <v>250.3935398321109</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +902,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9699657469700504</v>
+        <v>0.9999988556793131</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6784111618464707</v>
+        <v>0.6611192413365516</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9480178418896682</v>
+        <v>0.9999961815039328</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9197087130404763</v>
+        <v>0.9999975038822201</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9327441962625953</v>
+        <v>0.9999972200280685</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2008391883062913</v>
+        <v>6.79318191781452e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>2.150466041513092</v>
+        <v>0.2011742572291625</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3110076623417242</v>
+        <v>1.549412804030776e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8759770836521212</v>
+        <v>6.189477348996314e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5934923729969227</v>
+        <v>1.084180269465204e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>0.353146592291561</v>
+        <v>0.0003594086895972998</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4481508544076328</v>
+        <v>0.0008242076144888811</v>
       </c>
       <c r="N9" t="n">
-        <v>1.008191159917259</v>
+        <v>1.000000610304366</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4672295640799248</v>
+        <v>0.000859295838982642</v>
       </c>
       <c r="P9" t="n">
-        <v>227.2105014986361</v>
+        <v>166.4043524018402</v>
       </c>
       <c r="Q9" t="n">
-        <v>363.7245938838746</v>
+        <v>250.5067843177461</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +957,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9687085835625964</v>
+        <v>0.9999988926697259</v>
       </c>
       <c r="C10" t="n">
-        <v>0.676407027675503</v>
+        <v>0.6610729206822036</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9423738083980848</v>
+        <v>0.9999955948479446</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9167900726081548</v>
+        <v>0.9999974237167797</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9290266421519324</v>
+        <v>0.9999968893552131</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2092458458006422</v>
+        <v>6.573590848828318e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>2.163867695942543</v>
+        <v>0.2012017551705316</v>
       </c>
       <c r="I10" t="n">
-        <v>0.344775742125369</v>
+        <v>1.787457385861392e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9078194196134688</v>
+        <v>6.388258905515172e-07</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6262975717794137</v>
+        <v>1.213141638206455e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3370427979902496</v>
+        <v>0.0003519338928581504</v>
       </c>
       <c r="M10" t="n">
-        <v>0.457433979717994</v>
+        <v>0.000810776840371524</v>
       </c>
       <c r="N10" t="n">
-        <v>1.008534022664746</v>
+        <v>1.000000590576146</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4769078912534667</v>
+        <v>0.0008452932890055739</v>
       </c>
       <c r="P10" t="n">
-        <v>227.1284908452284</v>
+        <v>166.4700708308681</v>
       </c>
       <c r="Q10" t="n">
-        <v>363.6425832304669</v>
+        <v>250.5725027467739</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1012,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9674847510113378</v>
+        <v>0.9999989070548364</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6744878097558327</v>
+        <v>0.6610312002874557</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9369923545610964</v>
+        <v>0.9999950321525167</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9140851393287497</v>
+        <v>0.9999972727485852</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9255302119594505</v>
+        <v>0.9999965486384513</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2174296197061392</v>
+        <v>6.488194618608345e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>2.176701515008564</v>
+        <v>0.2012265221990812</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3769728158653492</v>
+        <v>2.015779606264926e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9373302128177344</v>
+        <v>6.762605912545984e-07</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6571514838084235</v>
+        <v>1.346020098759762e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3223933338897609</v>
+        <v>0.0003452128171095915</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4662934909540762</v>
+        <v>0.0008054933034239543</v>
       </c>
       <c r="N11" t="n">
-        <v>1.008867795178726</v>
+        <v>1.000000582904087</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4861445702245855</v>
+        <v>0.0008397848209517169</v>
       </c>
       <c r="P11" t="n">
-        <v>227.0517601367543</v>
+        <v>166.4962226757844</v>
       </c>
       <c r="Q11" t="n">
-        <v>363.5658525219927</v>
+        <v>250.5986545916903</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1067,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9663101519452094</v>
+        <v>0.9999989051726113</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6726669211380406</v>
+        <v>0.6609935576910089</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9319145512590719</v>
+        <v>0.9999944956409165</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9115881748516983</v>
+        <v>0.9999970774169306</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9222652714248709</v>
+        <v>0.9999962074395549</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2252841690698713</v>
+        <v>6.499368320336741e-07</v>
       </c>
       <c r="H12" t="n">
-        <v>2.188877805580161</v>
+        <v>0.2012488684704075</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4073531577403797</v>
+        <v>2.2334773407684e-06</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9645720686083019</v>
+        <v>7.246958398543215e-07</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6859626376105123</v>
+        <v>1.479086590311361e-06</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3090975399073834</v>
+        <v>0.0003391411687871779</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4746410950074501</v>
+        <v>0.000806186598768346</v>
       </c>
       <c r="N12" t="n">
-        <v>1.009188140378579</v>
+        <v>1.000000583907941</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4948475490644341</v>
+        <v>0.0008405076313142384</v>
       </c>
       <c r="P12" t="n">
-        <v>226.9807854000283</v>
+        <v>166.4927813205316</v>
       </c>
       <c r="Q12" t="n">
-        <v>363.4948777852668</v>
+        <v>250.5952132364375</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1122,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9651946603453332</v>
+        <v>0.9999988911977441</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6709521436526011</v>
+        <v>0.6609596370493118</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9271600165515157</v>
+        <v>0.9999939904261028</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9092900806911959</v>
+        <v>0.9999968495216367</v>
       </c>
       <c r="F13" t="n">
-        <v>0.919232875011301</v>
+        <v>0.999995872169593</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2327434665346099</v>
+        <v>6.582329168359331e-07</v>
       </c>
       <c r="H13" t="n">
-        <v>2.200344530521118</v>
+        <v>0.2012690052286143</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4357993935003708</v>
+        <v>2.438475928463645e-06</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9896442513681786</v>
+        <v>7.81205703711386e-07</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7127217281773839</v>
+        <v>1.609840816087516e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2970385610215911</v>
+        <v>0.0003336653184961363</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4824349350271079</v>
+        <v>0.0008113155470197358</v>
       </c>
       <c r="N13" t="n">
-        <v>1.009492365360364</v>
+        <v>1.000000591361203</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5029731889892017</v>
+        <v>0.0008458549295110764</v>
       </c>
       <c r="P13" t="n">
-        <v>226.9156368679235</v>
+        <v>166.4674139826037</v>
       </c>
       <c r="Q13" t="n">
-        <v>363.429729253162</v>
+        <v>250.5698458985095</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1177,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9641438670936335</v>
+        <v>0.9999988689656967</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6693472016681414</v>
+        <v>0.6609290659868581</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9227354104870388</v>
+        <v>0.9999935186702685</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9071801464958337</v>
+        <v>0.9999966032038254</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9164286120869107</v>
+        <v>0.9999955484489109</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2397701258471836</v>
+        <v>6.71430820564505e-07</v>
       </c>
       <c r="H14" t="n">
-        <v>2.211076784961279</v>
+        <v>0.2012871535318879</v>
       </c>
       <c r="I14" t="n">
-        <v>0.462271676278151</v>
+        <v>2.629898026913906e-06</v>
       </c>
       <c r="J14" t="n">
-        <v>1.012663610916905</v>
+        <v>8.422836915301536e-07</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7374676767055117</v>
+        <v>1.73609085922203e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2861221839527877</v>
+        <v>0.000328735380487302</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4896632780260162</v>
+        <v>0.0008194088238263639</v>
       </c>
       <c r="N14" t="n">
-        <v>1.0097789453381</v>
+        <v>1.000000603218295</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5105092575143063</v>
+        <v>0.0008542927538667554</v>
       </c>
       <c r="P14" t="n">
-        <v>226.8561492472047</v>
+        <v>166.4277096970645</v>
       </c>
       <c r="Q14" t="n">
-        <v>363.3702416324431</v>
+        <v>250.5301416129704</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1232,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9631605375816599</v>
+        <v>0.999998840612513</v>
       </c>
       <c r="C15" t="n">
-        <v>0.667852493147822</v>
+        <v>0.6609015010116983</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9186369134990087</v>
+        <v>0.9999930751890741</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9052475546652836</v>
+        <v>0.9999963490863516</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9138445445284377</v>
+        <v>0.9999952369575947</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2463456548215673</v>
+        <v>6.882624952324668e-07</v>
       </c>
       <c r="H15" t="n">
-        <v>2.221071907719154</v>
+        <v>0.2013035172918877</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4867928584240779</v>
+        <v>2.809847260571722e-06</v>
       </c>
       <c r="J15" t="n">
-        <v>1.033748167158589</v>
+        <v>9.05295716076247e-07</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7602705324003223</v>
+        <v>1.857571488323985e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2762408678016571</v>
+        <v>0.0003243314455334066</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4963322020799852</v>
+        <v>0.000829615872095313</v>
       </c>
       <c r="N15" t="n">
-        <v>1.010047126114093</v>
+        <v>1.000000618339993</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5174620914718288</v>
+        <v>0.0008649343373120164</v>
       </c>
       <c r="P15" t="n">
-        <v>226.8020392567593</v>
+        <v>166.3781910760209</v>
       </c>
       <c r="Q15" t="n">
-        <v>363.3161316419977</v>
+        <v>250.4806229919267</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1287,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9622451727234825</v>
+        <v>0.9999988087830319</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6664663248650322</v>
+        <v>0.6608767078183687</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9148553913410649</v>
+        <v>0.9999926652635417</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9034804923405643</v>
+        <v>0.9999960941795532</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9114702514797124</v>
+        <v>0.9999949426715405</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2524667038430665</v>
+        <v>7.071578501368416e-07</v>
       </c>
       <c r="H16" t="n">
-        <v>2.230341221408888</v>
+        <v>0.2013182356024583</v>
       </c>
       <c r="I16" t="n">
-        <v>0.509417589854799</v>
+        <v>2.976180774436365e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>1.053026798258617</v>
+        <v>9.685034648488308e-07</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7812222531050493</v>
+        <v>1.972342119642598e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2673059447005734</v>
+        <v>0.0003244963391230226</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5024606490493226</v>
+        <v>0.0008409267804849847</v>
       </c>
       <c r="N16" t="n">
-        <v>1.010296771075414</v>
+        <v>1.000000635315716</v>
       </c>
       <c r="O16" t="n">
-        <v>0.523851439116285</v>
+        <v>0.0008767267744886445</v>
       </c>
       <c r="P16" t="n">
-        <v>226.7529518098597</v>
+        <v>166.3240238569001</v>
       </c>
       <c r="Q16" t="n">
-        <v>363.2670441950982</v>
+        <v>250.4264557728059</v>
       </c>
     </row>
     <row r="17">
@@ -1342,52 +1342,52 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9613966551467943</v>
+        <v>0.9999987749208632</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6651854437417394</v>
+        <v>0.6608543348506398</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9113770272369874</v>
+        <v>0.9999922872276475</v>
       </c>
       <c r="E17" t="n">
-        <v>0.901867190338335</v>
+        <v>0.9999958418463544</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9092937928133041</v>
+        <v>0.9999946657931474</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2581407447854457</v>
+        <v>7.272598962460142e-07</v>
       </c>
       <c r="H17" t="n">
-        <v>2.238906479378262</v>
+        <v>0.2013315171625641</v>
       </c>
       <c r="I17" t="n">
-        <v>0.530228535919916</v>
+        <v>3.129574583001019e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>1.070627905881607</v>
+        <v>1.031073053143212e-06</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8004282033260854</v>
+        <v>2.080323818072116e-06</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2592350525878284</v>
+        <v>0.0003249166621836568</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5080755305911177</v>
+        <v>0.0008527953425330219</v>
       </c>
       <c r="N17" t="n">
-        <v>1.010528184959965</v>
+        <v>1.00000065337554</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5297053577897213</v>
+        <v>0.0008891006057943771</v>
       </c>
       <c r="P17" t="n">
-        <v>226.7085006407592</v>
+        <v>166.2679638638003</v>
       </c>
       <c r="Q17" t="n">
-        <v>363.2225930259976</v>
+        <v>250.3703957797062</v>
       </c>
     </row>
     <row r="18">
@@ -1397,52 +1397,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9606131521631819</v>
+        <v>0.9999987402672954</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6640056233299801</v>
+        <v>0.6608341653206464</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9081866297402561</v>
+        <v>0.9999919397555508</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9003965765419271</v>
+        <v>0.9999955987860961</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9073031534383911</v>
+        <v>0.9999944077624483</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2633800328445614</v>
+        <v>7.478317510646664e-07</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24679594390427</v>
+        <v>0.2013434906668465</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5493165865793994</v>
+        <v>3.270566666356516e-06</v>
       </c>
       <c r="J18" t="n">
-        <v>1.086672286702222</v>
+        <v>1.091343284584401e-06</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8179944090770573</v>
+        <v>2.180954975470458e-06</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2519394291758988</v>
+        <v>0.0003253486173921379</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5132056438159671</v>
+        <v>0.0008647726586014768</v>
       </c>
       <c r="N18" t="n">
-        <v>1.01074186759186</v>
+        <v>1.000000671857442</v>
       </c>
       <c r="O18" t="n">
-        <v>0.535053870555351</v>
+        <v>0.0009015878210043285</v>
       </c>
       <c r="P18" t="n">
-        <v>226.668314595992</v>
+        <v>166.2121756320092</v>
       </c>
       <c r="Q18" t="n">
-        <v>363.1824069812305</v>
+        <v>250.314607547915</v>
       </c>
     </row>
     <row r="19">
@@ -1452,52 +1452,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9598918465798016</v>
+        <v>0.9999987058197394</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6629217987242886</v>
+        <v>0.6608159686690367</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9052664267185513</v>
+        <v>0.9999916212416059</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8990577872192449</v>
+        <v>0.9999953641064253</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9054855848718765</v>
+        <v>0.9999941674604766</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2682034066019317</v>
+        <v>7.682813083975856e-07</v>
       </c>
       <c r="H19" t="n">
-        <v>2.254043484033083</v>
+        <v>0.2013542929852964</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5667880719574404</v>
+        <v>3.399808539540426e-06</v>
       </c>
       <c r="J19" t="n">
-        <v>1.101278463921663</v>
+        <v>1.149535430739084e-06</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8340333681212042</v>
+        <v>2.274671985139755e-06</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2453539612689339</v>
+        <v>0.000325611739738216</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5178835840243748</v>
+        <v>0.0008765165762252221</v>
       </c>
       <c r="N19" t="n">
-        <v>1.010938587296418</v>
+        <v>1.000000690229472</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5399309603631018</v>
+        <v>0.0009138317015145775</v>
       </c>
       <c r="P19" t="n">
-        <v>226.6320192129858</v>
+        <v>166.1582197677788</v>
       </c>
       <c r="Q19" t="n">
-        <v>363.1461115982243</v>
+        <v>250.2606516836847</v>
       </c>
     </row>
     <row r="20">
@@ -1507,52 +1507,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9592296400914591</v>
+        <v>0.9999986714579537</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6619284065908961</v>
+        <v>0.6607996164981276</v>
       </c>
       <c r="D20" t="n">
-        <v>0.90259952369042</v>
+        <v>0.9999913249512035</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8978402820592418</v>
+        <v>0.9999951417981972</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9038288894456057</v>
+        <v>0.9999939426524951</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2726315844386585</v>
+        <v>7.886799486780082e-07</v>
       </c>
       <c r="H20" t="n">
-        <v>2.260686301803228</v>
+        <v>0.2013640003403251</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5827440712199319</v>
+        <v>3.520032872643199e-06</v>
       </c>
       <c r="J20" t="n">
-        <v>1.114561432220933</v>
+        <v>1.204659902578975e-06</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8486527176082694</v>
+        <v>2.362346387611087e-06</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2394172570278262</v>
+        <v>0.0003260744910275345</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5221413452683655</v>
+        <v>0.0008880765443800484</v>
       </c>
       <c r="N20" t="n">
-        <v>1.011119189065966</v>
+        <v>1.000000708555758</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5443699833180301</v>
+        <v>0.0009258838014461878</v>
       </c>
       <c r="P20" t="n">
-        <v>226.5992678055065</v>
+        <v>166.1058104802432</v>
       </c>
       <c r="Q20" t="n">
-        <v>363.113360190745</v>
+        <v>250.2082423961491</v>
       </c>
     </row>
     <row r="21">
@@ -1562,52 +1562,52 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9586228747746665</v>
+        <v>0.9999986385671662</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6610197621490205</v>
+        <v>0.6607849052022134</v>
       </c>
       <c r="D21" t="n">
-        <v>0.900166603238863</v>
+        <v>0.9999910559277282</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8967342788403494</v>
+        <v>0.9999949327631036</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9023204221637456</v>
+        <v>0.9999937362488057</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2766890269059484</v>
+        <v>8.082053409766694e-07</v>
       </c>
       <c r="H21" t="n">
-        <v>2.266762411369974</v>
+        <v>0.2013727336010746</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5973001598820474</v>
+        <v>3.629193235780107e-06</v>
       </c>
       <c r="J21" t="n">
-        <v>1.126627915532922</v>
+        <v>1.256493112810844e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>0.861964042088084</v>
+        <v>2.442843174295475e-06</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2340585572455786</v>
+        <v>0.0003263626751994648</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5260123828446898</v>
+        <v>0.0008990024143330592</v>
       </c>
       <c r="N21" t="n">
-        <v>1.011284670516</v>
+        <v>1.000000726097511</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5484058189781308</v>
+        <v>0.0009372748083027669</v>
       </c>
       <c r="P21" t="n">
-        <v>226.5697220999668</v>
+        <v>166.05689935168</v>
       </c>
       <c r="Q21" t="n">
-        <v>363.0838144852053</v>
+        <v>250.1593312675858</v>
       </c>
     </row>
     <row r="22">
@@ -1617,52 +1617,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9580683821047449</v>
+        <v>0.9999986069290061</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6601900697136782</v>
+        <v>0.6607716233783558</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8979519539929377</v>
+        <v>0.9999908089148704</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8957306827615008</v>
+        <v>0.9999947358075937</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9009492557163047</v>
+        <v>0.9999935451355559</v>
       </c>
       <c r="G22" t="n">
-        <v>0.280396921942918</v>
+        <v>8.269871194795217e-07</v>
       </c>
       <c r="H22" t="n">
-        <v>2.27231056850549</v>
+        <v>0.2013806182654614</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6105503385956776</v>
+        <v>3.72942245636342e-06</v>
       </c>
       <c r="J22" t="n">
-        <v>1.137577138040188</v>
+        <v>1.305331019302608e-06</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8740637685569378</v>
+        <v>2.517376737833014e-06</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2292249010985154</v>
+        <v>0.0003266102584847785</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5295251853716857</v>
+        <v>0.0009093883216093781</v>
       </c>
       <c r="N22" t="n">
-        <v>1.011435895789615</v>
+        <v>1.000000742971197</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5520681687812047</v>
+        <v>0.0009481028651536307</v>
       </c>
       <c r="P22" t="n">
-        <v>226.543098202522</v>
+        <v>166.0109534340771</v>
       </c>
       <c r="Q22" t="n">
-        <v>363.0571905877605</v>
+        <v>250.1133853499829</v>
       </c>
     </row>
     <row r="23">
@@ -1672,52 +1672,52 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9575622428785251</v>
+        <v>0.9999985773084966</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6594338097666231</v>
+        <v>0.6607596863195675</v>
       </c>
       <c r="D23" t="n">
-        <v>0.895937753973106</v>
+        <v>0.9999905868959645</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8948204724035643</v>
+        <v>0.9999945537107964</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8997037630893199</v>
+        <v>0.9999933717482241</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2837814772792065</v>
+        <v>8.445711334911774e-07</v>
       </c>
       <c r="H23" t="n">
-        <v>2.277367682253704</v>
+        <v>0.2013877046192122</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6226012357193969</v>
+        <v>3.819510001114027e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>1.147507523329155</v>
+        <v>1.350484497688932e-06</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8850544984815323</v>
+        <v>2.58499724940148e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2248679684578168</v>
+        <v>0.0003268705906326325</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5327114390354374</v>
+        <v>0.0009190055133083682</v>
       </c>
       <c r="N23" t="n">
-        <v>1.011573933760402</v>
+        <v>1.000000758768802</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5553900678598767</v>
+        <v>0.0009581294806135781</v>
       </c>
       <c r="P23" t="n">
-        <v>226.5191015663931</v>
+        <v>165.9688737455167</v>
       </c>
       <c r="Q23" t="n">
-        <v>363.0331939516316</v>
+        <v>250.0713056614225</v>
       </c>
     </row>
     <row r="24">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9571010431685057</v>
+        <v>0.9999985493028015</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6587453491025941</v>
+        <v>0.6607489232071986</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8941079610002265</v>
+        <v>0.9999903835556669</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8939956469704431</v>
+        <v>0.9999943845601994</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8985735936820547</v>
+        <v>0.9999932121934694</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2868655218637352</v>
+        <v>8.611965238464195e-07</v>
       </c>
       <c r="H24" t="n">
-        <v>2.281971421884137</v>
+        <v>0.2013940940676567</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6335488311204324</v>
+        <v>3.902018416761316e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>1.156506359999837</v>
+        <v>1.392427782468428e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8950275697427907</v>
+        <v>2.647223099614872e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2209419004916959</v>
+        <v>0.0003270596892418514</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5355982840373326</v>
+        <v>0.0009280067477375471</v>
       </c>
       <c r="N24" t="n">
-        <v>1.011699715499498</v>
+        <v>1.000000773705173</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5583998118300955</v>
+        <v>0.0009675139162275312</v>
       </c>
       <c r="P24" t="n">
-        <v>226.4974834759362</v>
+        <v>165.9298862157424</v>
       </c>
       <c r="Q24" t="n">
-        <v>363.0115758611747</v>
+        <v>250.0323181316483</v>
       </c>
     </row>
     <row r="25">
@@ -1782,52 +1782,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9566814110940679</v>
+        <v>0.9999985230219011</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6581194237720067</v>
+        <v>0.6607392451792065</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8924475734365287</v>
+        <v>0.9999901978092807</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8932488949502548</v>
+        <v>0.9999942277136221</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8975490974649407</v>
+        <v>0.9999930657028624</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2896716034777294</v>
+        <v>8.767980016680298e-07</v>
       </c>
       <c r="H25" t="n">
-        <v>2.286156987451895</v>
+        <v>0.2013998393631419</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6434828791388101</v>
+        <v>3.977387835573215e-06</v>
       </c>
       <c r="J25" t="n">
-        <v>1.164653416568822</v>
+        <v>1.431320111377098e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9040681380987263</v>
+        <v>2.704353973475157e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2174024828467412</v>
+        <v>0.0003272908443221658</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5382114858285072</v>
+        <v>0.0009363749258005736</v>
       </c>
       <c r="N25" t="n">
-        <v>1.011814160610709</v>
+        <v>1.000000787721653</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5611242630315938</v>
+        <v>0.0009762383449552173</v>
       </c>
       <c r="P25" t="n">
-        <v>226.4780147989079</v>
+        <v>165.8939783997495</v>
       </c>
       <c r="Q25" t="n">
-        <v>362.9921071841463</v>
+        <v>249.9964103156553</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9562999552811551</v>
+        <v>0.9999984989193815</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6575509239197632</v>
+        <v>0.6607304653565699</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8909421735437159</v>
+        <v>0.9999900317963561</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8925728747280407</v>
+        <v>0.999994084089042</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8966208656928564</v>
+        <v>0.9999929336812615</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2922224002551195</v>
+        <v>8.91106298421217e-07</v>
       </c>
       <c r="H26" t="n">
-        <v>2.289958548581549</v>
+        <v>0.2014050514451275</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6524896406618594</v>
+        <v>4.044750102377497e-06</v>
       </c>
       <c r="J26" t="n">
-        <v>1.172028789976942</v>
+        <v>1.466933858950551e-06</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9122592301159504</v>
+        <v>2.755841980664024e-06</v>
       </c>
       <c r="L26" t="n">
-        <v>0.214210119463722</v>
+        <v>0.0003274806863683464</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5405759893438845</v>
+        <v>0.0009439842681004895</v>
       </c>
       <c r="N26" t="n">
-        <v>1.01191819401423</v>
+        <v>1.00000080057633</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5635894283568178</v>
+        <v>0.0009841716327103507</v>
       </c>
       <c r="P26" t="n">
-        <v>226.4604802438174</v>
+        <v>165.8616042284217</v>
       </c>
       <c r="Q26" t="n">
-        <v>362.9745726290558</v>
+        <v>249.9640361443275</v>
       </c>
     </row>
   </sheetData>

--- a/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_9_6.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_9_6.xlsx
@@ -517,657 +517,657 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999970347421123</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6616188094088302</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999998540361883</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999925115415463</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999975434463748</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7603051745786e-06</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2008776920412408</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I2" t="n">
-        <v>5.922703460030875e-08</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.856869269182998e-06</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>9.580481518916534e-07</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004551402773565474</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001326764928153665</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000001581470873</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001383248057927192</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P2" t="n">
-        <v>164.5000467385968</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q2" t="n">
-        <v>248.6024786545026</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_1</t>
+          <t>model_9_6_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9999975854802722</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6615237926002615</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9999995379007756</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999943048349101</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999979490852062</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G3" t="n">
-        <v>1.433363212273532e-06</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2009340981233196</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I3" t="n">
-        <v>1.875037822389691e-07</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.412196796405519e-06</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>7.998502893222442e-07</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004313784758995392</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001197231478150125</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000001287743855</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001248200100785794</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P3" t="n">
-        <v>164.9109739567558</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q3" t="n">
-        <v>249.0134058726617</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_2</t>
+          <t>model_9_6_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9999979989458007</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6614379696158399</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999990952364693</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9999955763257784</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9999981230178837</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G4" t="n">
-        <v>1.187912213777347e-06</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2009850463542323</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I4" t="n">
-        <v>3.671215510817157e-07</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.096912638256701e-06</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.320170946692087e-07</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004111735884083415</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001089913856126871</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000001067228906</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001136313745414907</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P4" t="n">
-        <v>165.2866264677619</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q4" t="n">
-        <v>249.3890583836677</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_3</t>
+          <t>model_9_6_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9999983053104504</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6613604575020769</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9999985696206511</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9999964504993371</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9999981274885635</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G5" t="n">
-        <v>1.006040923382105e-06</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2010310608933109</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I5" t="n">
-        <v>5.803981564334399e-07</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>8.801489308776066e-07</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>7.302735436555232e-07</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003985767631041862</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001003015913822959</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000000903834426</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001045716377803578</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P5" t="n">
-        <v>165.6189756156157</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q5" t="n">
-        <v>249.7214075315215</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_4</t>
+          <t>model_9_6_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9999985273038922</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6612905126262505</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9999979929943462</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9999970124562274</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9999980061674265</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G6" t="n">
-        <v>8.74256026786897e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2010725831930628</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I6" t="n">
-        <v>8.143730419050571e-07</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>7.40803765682814e-07</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>7.775884037939356e-07</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000387195046877251</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009350165917174395</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000000785437924</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000974822183778025</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P6" t="n">
-        <v>165.8997851347227</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q6" t="n">
-        <v>250.0022170506286</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_5</t>
+          <t>model_9_6_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9999986836567488</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6612274951166779</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D7" t="n">
-        <v>0.999997391637693</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9999973388810905</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999977971042777</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G7" t="n">
-        <v>7.81438216953765e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2011099931089597</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0583826419722e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>6.598621004836274e-07</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>8.591223712279138e-07</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0003768968809856536</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0008839899416587075</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000000702049734</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009216232235865654</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P7" t="n">
-        <v>166.124259494422</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q7" t="n">
-        <v>250.2266914103278</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_6</t>
+          <t>model_9_6_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9999987890158003</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6611706058340938</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9999967827914558</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9999974875816573</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F8" t="n">
-        <v>0.999997527645425</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G8" t="n">
-        <v>7.188925327195555e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2011437650445907</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I8" t="n">
-        <v>1.305431254586434e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>6.229896901699325e-07</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>9.642104723781832e-07</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003677149860472127</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0008478753049355521</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N8" t="n">
-        <v>1.00000064585824</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0008839711120105012</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P8" t="n">
-        <v>166.2911079162051</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q8" t="n">
-        <v>250.3935398321109</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_7</t>
+          <t>model_9_6_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9999988556793131</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6611192413365516</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9999961815039328</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9999975038822201</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9999972200280685</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G9" t="n">
-        <v>6.79318191781452e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2011742572291625</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I9" t="n">
-        <v>1.549412804030776e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>6.189477348996314e-07</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.084180269465204e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003594086895972998</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0008242076144888811</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000000610304366</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O9" t="n">
-        <v>0.000859295838982642</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P9" t="n">
-        <v>166.4043524018402</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q9" t="n">
-        <v>250.5067843177461</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_8</t>
+          <t>model_9_6_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9999988926697259</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6610729206822036</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9999955948479446</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9999974237167797</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9999968893552131</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G10" t="n">
-        <v>6.573590848828318e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2012017551705316</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I10" t="n">
-        <v>1.787457385861392e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>6.388258905515172e-07</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>1.213141638206455e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0003519338928581504</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M10" t="n">
-        <v>0.000810776840371524</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000000590576146</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0008452932890055739</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P10" t="n">
-        <v>166.4700708308681</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q10" t="n">
-        <v>250.5725027467739</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_9</t>
+          <t>model_9_6_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9999989070548364</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6610312002874557</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9999950321525167</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9999972727485852</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9999965486384513</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G11" t="n">
-        <v>6.488194618608345e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2012265221990812</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I11" t="n">
-        <v>2.015779606264926e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>6.762605912545984e-07</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K11" t="n">
-        <v>1.346020098759762e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0003452128171095915</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0008054933034239543</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000000582904087</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0008397848209517169</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P11" t="n">
-        <v>166.4962226757844</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q11" t="n">
-        <v>250.5986545916903</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_10</t>
+          <t>model_9_6_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9999989051726113</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6609935576910089</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9999944956409165</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9999970774169306</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9999962074395549</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G12" t="n">
-        <v>6.499368320336741e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2012488684704075</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2334773407684e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J12" t="n">
-        <v>7.246958398543215e-07</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K12" t="n">
-        <v>1.479086590311361e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0003391411687871779</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M12" t="n">
-        <v>0.000806186598768346</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000000583907941</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0008405076313142384</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P12" t="n">
-        <v>166.4927813205316</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q12" t="n">
-        <v>250.5952132364375</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_11</t>
+          <t>model_9_6_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9999988911977441</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6609596370493118</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9999939904261028</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9999968495216367</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F13" t="n">
-        <v>0.999995872169593</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G13" t="n">
-        <v>6.582329168359331e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2012690052286143</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I13" t="n">
-        <v>2.438475928463645e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J13" t="n">
-        <v>7.81205703711386e-07</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K13" t="n">
-        <v>1.609840816087516e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0003336653184961363</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0008113155470197358</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000000591361203</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0008458549295110764</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P13" t="n">
-        <v>166.4674139826037</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q13" t="n">
-        <v>250.5698458985095</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="14">
@@ -1177,657 +1177,657 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9999988689656967</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6609290659868581</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9999935186702685</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9999966032038254</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9999955484489109</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G14" t="n">
-        <v>6.71430820564505e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2012871535318879</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I14" t="n">
-        <v>2.629898026913906e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J14" t="n">
-        <v>8.422836915301536e-07</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K14" t="n">
-        <v>1.73609085922203e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L14" t="n">
-        <v>0.000328735380487302</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0008194088238263639</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000000603218295</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0008542927538667554</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P14" t="n">
-        <v>166.4277096970645</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q14" t="n">
-        <v>250.5301416129704</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_13</t>
+          <t>model_9_6_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.999998840612513</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6609015010116983</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9999930751890741</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9999963490863516</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9999952369575947</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G15" t="n">
-        <v>6.882624952324668e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2013035172918877</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I15" t="n">
-        <v>2.809847260571722e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J15" t="n">
-        <v>9.05295716076247e-07</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K15" t="n">
-        <v>1.857571488323985e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0003243314455334066</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M15" t="n">
-        <v>0.000829615872095313</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000000618339993</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0008649343373120164</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P15" t="n">
-        <v>166.3781910760209</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q15" t="n">
-        <v>250.4806229919267</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_14</t>
+          <t>model_9_6_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9999988087830319</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6608767078183687</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9999926652635417</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9999960941795532</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9999949426715405</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G16" t="n">
-        <v>7.071578501368416e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2013182356024583</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I16" t="n">
-        <v>2.976180774436365e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J16" t="n">
-        <v>9.685034648488308e-07</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K16" t="n">
-        <v>1.972342119642598e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0003244963391230226</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0008409267804849847</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000000635315716</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0008767267744886445</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P16" t="n">
-        <v>166.3240238569001</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q16" t="n">
-        <v>250.4264557728059</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_15</t>
+          <t>model_9_6_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9999987749208632</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6608543348506398</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9999922872276475</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9999958418463544</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9999946657931474</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G17" t="n">
-        <v>7.272598962460142e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2013315171625641</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I17" t="n">
-        <v>3.129574583001019e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J17" t="n">
-        <v>1.031073053143212e-06</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K17" t="n">
-        <v>2.080323818072116e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0003249166621836568</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0008527953425330219</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N17" t="n">
-        <v>1.00000065337554</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0008891006057943771</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P17" t="n">
-        <v>166.2679638638003</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q17" t="n">
-        <v>250.3703957797062</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_16</t>
+          <t>model_9_6_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9999987402672954</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6608341653206464</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9999919397555508</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9999955987860961</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9999944077624483</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G18" t="n">
-        <v>7.478317510646664e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2013434906668465</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I18" t="n">
-        <v>3.270566666356516e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J18" t="n">
-        <v>1.091343284584401e-06</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K18" t="n">
-        <v>2.180954975470458e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0003253486173921379</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0008647726586014768</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000000671857442</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0009015878210043285</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P18" t="n">
-        <v>166.2121756320092</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q18" t="n">
-        <v>250.314607547915</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_17</t>
+          <t>model_9_6_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9999987058197394</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6608159686690367</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9999916212416059</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9999953641064253</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9999941674604766</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G19" t="n">
-        <v>7.682813083975856e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2013542929852964</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I19" t="n">
-        <v>3.399808539540426e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J19" t="n">
-        <v>1.149535430739084e-06</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K19" t="n">
-        <v>2.274671985139755e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L19" t="n">
-        <v>0.000325611739738216</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0008765165762252221</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000000690229472</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0009138317015145775</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P19" t="n">
-        <v>166.1582197677788</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q19" t="n">
-        <v>250.2606516836847</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_18</t>
+          <t>model_9_6_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9999986714579537</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6607996164981276</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9999913249512035</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9999951417981972</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9999939426524951</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G20" t="n">
-        <v>7.886799486780082e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2013640003403251</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I20" t="n">
-        <v>3.520032872643199e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J20" t="n">
-        <v>1.204659902578975e-06</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K20" t="n">
-        <v>2.362346387611087e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0003260744910275345</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0008880765443800484</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000000708555758</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0009258838014461878</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P20" t="n">
-        <v>166.1058104802432</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q20" t="n">
-        <v>250.2082423961491</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_19</t>
+          <t>model_9_6_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9999986385671662</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6607849052022134</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9999910559277282</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9999949327631036</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9999937362488057</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G21" t="n">
-        <v>8.082053409766694e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2013727336010746</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I21" t="n">
-        <v>3.629193235780107e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J21" t="n">
-        <v>1.256493112810844e-06</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K21" t="n">
-        <v>2.442843174295475e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0003263626751994648</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0008990024143330592</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000000726097511</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0009372748083027669</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P21" t="n">
-        <v>166.05689935168</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q21" t="n">
-        <v>250.1593312675858</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_20</t>
+          <t>model_9_6_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9999986069290061</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6607716233783558</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9999908089148704</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9999947358075937</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9999935451355559</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G22" t="n">
-        <v>8.269871194795217e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2013806182654614</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I22" t="n">
-        <v>3.72942245636342e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J22" t="n">
-        <v>1.305331019302608e-06</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K22" t="n">
-        <v>2.517376737833014e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0003266102584847785</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0009093883216093781</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000000742971197</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0009481028651536307</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P22" t="n">
-        <v>166.0109534340771</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q22" t="n">
-        <v>250.1133853499829</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_21</t>
+          <t>model_9_6_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9999985773084966</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6607596863195675</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9999905868959645</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9999945537107964</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9999933717482241</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G23" t="n">
-        <v>8.445711334911774e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2013877046192122</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I23" t="n">
-        <v>3.819510001114027e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J23" t="n">
-        <v>1.350484497688932e-06</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K23" t="n">
-        <v>2.58499724940148e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0003268705906326325</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0009190055133083682</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000000758768802</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0009581294806135781</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P23" t="n">
-        <v>165.9688737455167</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q23" t="n">
-        <v>250.0713056614225</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_22</t>
+          <t>model_9_6_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9999985493028015</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6607489232071986</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9999903835556669</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9999943845601994</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9999932121934694</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G24" t="n">
-        <v>8.611965238464195e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2013940940676567</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I24" t="n">
-        <v>3.902018416761316e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J24" t="n">
-        <v>1.392427782468428e-06</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K24" t="n">
-        <v>2.647223099614872e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0003270596892418514</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0009280067477375471</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000000773705173</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0009675139162275312</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P24" t="n">
-        <v>165.9298862157424</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q24" t="n">
-        <v>250.0323181316483</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_9_6_23</t>
+          <t>model_9_6_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9999985230219011</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6607392451792065</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9999901978092807</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9999942277136221</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9999930657028624</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G25" t="n">
-        <v>8.767980016680298e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2013998393631419</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I25" t="n">
-        <v>3.977387835573215e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J25" t="n">
-        <v>1.431320111377098e-06</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K25" t="n">
-        <v>2.704353973475157e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0003272908443221658</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0009363749258005736</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000000787721653</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0009762383449552173</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P25" t="n">
-        <v>165.8939783997495</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q25" t="n">
-        <v>249.9964103156553</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9999984989193815</v>
+        <v>0.9999988272735516</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6607304653565699</v>
+        <v>0.6979243459510645</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9999900317963561</v>
+        <v>0.9999984042787953</v>
       </c>
       <c r="E26" t="n">
-        <v>0.999994084089042</v>
+        <v>0.9999999897550887</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9999929336812615</v>
+        <v>0.9999991408974288</v>
       </c>
       <c r="G26" t="n">
-        <v>8.91106298421217e-07</v>
+        <v>6.96181078937286e-07</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2014050514451275</v>
+        <v>0.179325157232253</v>
       </c>
       <c r="I26" t="n">
-        <v>4.044750102377497e-06</v>
+        <v>7.931514618997071e-07</v>
       </c>
       <c r="J26" t="n">
-        <v>1.466933858950551e-06</v>
+        <v>4.185318684476582e-09</v>
       </c>
       <c r="K26" t="n">
-        <v>2.755841980664024e-06</v>
+        <v>3.986683902920918e-07</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0003274806863683464</v>
+        <v>0.0001792738584187023</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0009439842681004895</v>
+        <v>0.0008343746634080436</v>
       </c>
       <c r="N26" t="n">
-        <v>1.00000080057633</v>
+        <v>1.000000625454106</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0009841716327103507</v>
+        <v>0.0008698957202229859</v>
       </c>
       <c r="P26" t="n">
-        <v>165.8616042284217</v>
+        <v>166.3553120791273</v>
       </c>
       <c r="Q26" t="n">
-        <v>249.9640361443275</v>
+        <v>250.4577439950332</v>
       </c>
     </row>
   </sheetData>
